--- a/AAII_Financials/Quarterly/BR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>BR</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2219900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1953600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1713900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1589400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2065400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1811700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1589200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1422900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1944300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1726500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1405000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1431100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1839000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1645700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1292900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1283300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1722900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1533700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1259600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1192900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1531600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1389800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1054900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1017400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1361900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1249900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>968700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>948600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1211200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1224800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>953400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>972800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1320400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1071900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1012800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>924800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1345800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1008900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>892600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>895300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1366900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1326700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1240300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1166800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1295600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1235900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1145800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1075000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1253100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1187300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1057200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1075300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1159100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1137700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>988200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>990400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1146800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1077600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>978400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>914100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1016700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>960500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>806500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>787100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>884200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>872500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>780900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>727500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>811600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>847300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>734000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>739000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>870100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>803100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>769800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>726600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>910100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>773700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>707800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>717900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>853000</v>
+      </c>
+      <c r="E10" s="3">
         <v>626900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>473600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>422600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>769800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>575800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>443400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>347900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>691200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>539200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>347800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>355800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>679900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>508000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>304700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>292900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>576100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>456100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>281200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>278800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>514900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>429300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>248400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>230300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>477700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>377400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>187800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>221100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>399600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>377500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>219400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>233800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>450300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>268800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>243000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>198200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>435700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>235200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>184800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>177400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,13 +1496,16 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-227000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1517,14 +1537,14 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1601,53 +1621,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E15" s="3">
         <v>130000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>126900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>126100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>125900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>123500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>125400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>123300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>120100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>120300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>118000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>119500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>103200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>105700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1673600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1594100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1507800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1566700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1466800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1378600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1288400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1502900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1423500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1280600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1282600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1384800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1358900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1185000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1195800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1381200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1287700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1190700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1089600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1250200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1150600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>975400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>938800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1063100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1023600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>941900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>875500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>970400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>991200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>875200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>872700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1055000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>941900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>897700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>840400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1048700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>899200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>833800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>829300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>546300</v>
+      </c>
+      <c r="E18" s="3">
         <v>359500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>206100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>188700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>498700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>344900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>210600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>134500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>441400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>303000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>124400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>148500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>454200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>286800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>107900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>87500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>341700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>246000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>68900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>103300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>281400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>239200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>79500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>78600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>298800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>226300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>26800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>73100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>240800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>233600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>78200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>100100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>265400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>130000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>115100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>84400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>297100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>109700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>58800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>66000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>224500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-188000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-48600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1900</v>
       </c>
       <c r="J20" s="3">
         <v>1900</v>
       </c>
       <c r="K20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>73200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>12100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>8300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>447200</v>
+      </c>
+      <c r="E21" s="3">
         <v>495700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>521000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>363400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>624000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>465500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>334100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>255900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>563300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>422200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>242000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>265900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>556700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>394300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>183600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>160000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>418600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>325700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>157900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>190400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>431300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>277000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>130000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>136400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>360200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>274800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>77200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>126600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>287300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>277600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>118200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>142600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>312500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>176600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>154700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>123100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>333100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>157700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>106200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>99900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E22" s="3">
         <v>27400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>36500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>38200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>40000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>36400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>40300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>36300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>15500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>14200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>10500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>10800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>10000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>11300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>11700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>11000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>522000</v>
+      </c>
+      <c r="E23" s="3">
         <v>340600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>370300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>213100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>471500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>310900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>176000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>100300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>410200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>266600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>87700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>112900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>417500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>250100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>71900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>55400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>318800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>223300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>51900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>78300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>336300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>216800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>69400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>73700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>294700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>210500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>63800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>230100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>223600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>64300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>89300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>258000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>125200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>103500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>74300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>284600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>106300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>45700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E24" s="3">
         <v>64300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>85700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>47700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>97300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>67800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>33600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>87000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>52900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>22000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>93400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>51600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>70700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>46800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>76000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>51900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>65000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>43600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>46300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>51400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>12600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>51800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>16200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>25300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>24400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>97600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>30400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>15600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>17900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>398100</v>
+      </c>
+      <c r="E26" s="3">
         <v>276300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>284600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>165400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>374200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>243100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>142400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>79800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>323200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>213700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>70300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>90900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>324100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>198500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>57500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>50400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>248100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>176500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>47200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>67300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>260300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>164900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>56300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>65900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>229700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>166900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>55900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>183800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>172200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>49900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>76700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>206200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>109000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>78200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>49900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>187000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>75900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>30100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>398100</v>
+      </c>
+      <c r="E27" s="3">
         <v>276300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>284600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>165400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>374200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>243100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>142400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>79800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>323200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>213700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>70300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>90900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>324100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>198500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>57500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>50400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>248100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>176600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>47200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>67200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>260400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>165000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>56300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>65800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>229700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>166800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>55900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>183800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>172200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>49900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>76700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>206200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>109100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>78200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>49900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>187100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>75900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>30100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3218,8 +3279,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3236,29 +3297,29 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-500</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>600</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-16100</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-224500</v>
+      </c>
+      <c r="E32" s="3">
         <v>6200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>188000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>48600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1900</v>
       </c>
       <c r="J32" s="3">
         <v>-1900</v>
       </c>
       <c r="K32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L32" s="3">
         <v>1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-73200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>10400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>398100</v>
+      </c>
+      <c r="E33" s="3">
         <v>276300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>284600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>165400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>374200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>243100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>142400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>79800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>323200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>213700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>70300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>90900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>324100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>198500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>57500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>50400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>248100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>176600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>47200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>67200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>260400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>165000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>56300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>65800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>229700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>166800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>55900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>183300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>172200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>49900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>76700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>206800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>109100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>62100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>49900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>187100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>75900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>30100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>398100</v>
+      </c>
+      <c r="E35" s="3">
         <v>276300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>284600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>165400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>374200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>243100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>142400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>79800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>323200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>213700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>70300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>90900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>324100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>198500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>57500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>50400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>248100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>176600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>47200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>67200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>260400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>165000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>56300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>65800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>229700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>166800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>55900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>183300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>172200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>49900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>76700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>206800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>109100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>62100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>49900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>187100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>75900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>30100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,135 +4305,139 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>402900</v>
+      </c>
+      <c r="E41" s="3">
         <v>304800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>370700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>290700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>561500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>317200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>289900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>292800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>304400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>235600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>277000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>234000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>252300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>331600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>280000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>227100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>224700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>277200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>281200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>316700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>274500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>355800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>365600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>356600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>476600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>402100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>234000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>358300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>273200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>292100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>249800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>204700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>263900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>352100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>366500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>288800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>271100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>269500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>235700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E42" s="3">
         <v>800</v>
@@ -4356,7 +4446,7 @@
         <v>800</v>
       </c>
       <c r="G42" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H42" s="3">
         <v>700</v>
@@ -4368,13 +4458,13 @@
         <v>700</v>
       </c>
       <c r="K42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L42" s="3">
         <v>800</v>
       </c>
       <c r="M42" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N42" s="3">
         <v>700</v>
@@ -4386,7 +4476,7 @@
         <v>700</v>
       </c>
       <c r="Q42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -4463,135 +4553,141 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1129400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1319300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1065000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>963700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1077100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1184200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1040300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>895300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1065600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1165100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>892200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>916200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>974000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1096200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>860200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>840100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>946900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>988000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>779500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>730000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>820300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>871000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>625000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>619100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>711300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>814700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>616000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>600700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>664000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>792800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>607400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>650100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>615000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>714100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>575100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>624400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>589500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>661200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>515500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>499400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>35100</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
@@ -4599,11 +4695,11 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>32100</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>8</v>
@@ -4611,11 +4707,11 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>30500</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
@@ -4623,15 +4719,15 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3">
         <v>34100</v>
       </c>
-      <c r="P44" s="3" t="s">
+      <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4707,618 +4803,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E45" s="3">
         <v>172800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>257400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>203800</v>
       </c>
-      <c r="G45" s="3">
-        <v>145700</v>
-      </c>
       <c r="H45" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I45" s="3">
         <v>163400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>177500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>161400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>139600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>163600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>193700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>176000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>131400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>139700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>142500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>154800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>156800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>229900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>205900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>164400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>166500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>151800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>157900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>144300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>140100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>144200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>160600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>136100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>105100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>110500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>109200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>113100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>112200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>136800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>109600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>121100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>129000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>187500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>148200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>159000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1748100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1797700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1693900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1459000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1817100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1665500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1508400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1350200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1540900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1565100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1363600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1326900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1392500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1568200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1282700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1222000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1328400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1495100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1266600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1211100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1261300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1378600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1148500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1120000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1328000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1361000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1010600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1095100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1042300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1195400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>966400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>967900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>991100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1203000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1051200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1034300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>989600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1118200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>899400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>885800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>320600</v>
+      </c>
+      <c r="E47" s="3">
         <v>548300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>548100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>401900</v>
       </c>
-      <c r="G47" s="3">
-        <v>299100</v>
-      </c>
       <c r="H47" s="3">
+        <v>232700</v>
+      </c>
+      <c r="I47" s="3">
         <v>280200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>284800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>285100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>271100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>262400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>256500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>243400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>241900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>233900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>338800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>334300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>340100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>330300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>311700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>290400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>283800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>257200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>259700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>245200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>223500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>211800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>204200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>193700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>147900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>131200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>120900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>126000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>80300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>78700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>76000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>73200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>63400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>60500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>56700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>57900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>402900</v>
+      </c>
+      <c r="E48" s="3">
         <v>304300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>315100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>332800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>346200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>333200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>337000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>342900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>348400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>330000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>326500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>335100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>344000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>345300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>354800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>359800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>373700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>407700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>414100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>422400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>439200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>422300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>423000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>426200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>454200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>451500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>373300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>414300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>189000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>183400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>187900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>192500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>204100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>197900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>202500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>207600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>198100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>169500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>145500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4987700</v>
+      </c>
+      <c r="E49" s="3">
         <v>4894200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4914900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4938300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4887000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4784500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4840900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4777100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4776600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4769100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4776900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4848200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4928800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4340100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4319400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4437300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4562000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4748900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4916800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5023500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5145100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2270100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2248600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2261900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2258300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2315900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2272000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2041900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2056200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1683700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1699700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1728800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1749000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1721500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1657200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1647200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1645700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1645400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1625500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1628500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>396400</v>
+      </c>
+      <c r="E52" s="3">
         <v>141200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>75200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>72900</v>
       </c>
-      <c r="G52" s="3">
-        <v>48400</v>
-      </c>
       <c r="H52" s="3">
+        <v>141600</v>
+      </c>
+      <c r="I52" s="3">
         <v>125300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>142600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>117300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>121200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>130700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>107300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>145400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>135900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>185600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1755600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1737200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1564600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1367500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1206700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1081000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>990400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>858600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>778500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>696400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>625800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>573300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>524500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>475100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>445300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>408400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>382700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>366500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>280200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>283600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>263000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>262200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>253000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>248400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>240200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>239400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8945300</v>
+      </c>
+      <c r="E54" s="3">
         <v>8779200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8639500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8302900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8545000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8299600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8230600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8017100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8242400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8215400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7999800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8071200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8233200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8432300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8051300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8090600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8168800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8349500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8115900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8028400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8119800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5186800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4858300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4749700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4889800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4913500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4384600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4220100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3880700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3602100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3357600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3381700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3304700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3484700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3249900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3224500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3149800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3242000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2967300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2942300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,174 +6145,178 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>149700</v>
+      </c>
+      <c r="E57" s="3">
         <v>235900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>194400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>152700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>220300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>206600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>198300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>168000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>314000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>158100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>136500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>143200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>157300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>183800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>169800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>167100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>245000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>197600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>192200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>157100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>248900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>182400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>131600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>119900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>151500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>146600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>92600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>89600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>133700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>151900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>137500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>128500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>191800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>147400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>134300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>157300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>167200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>191900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>140600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>134100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E58" s="3">
         <v>538700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>538600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>537600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>536500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>38000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>38500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>39500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>38000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>36600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>39100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>40100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1219400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>38900</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -6196,8 +6330,8 @@
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -6212,19 +6346,19 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>399900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>399800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>399500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>399400</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
@@ -6247,508 +6381,523 @@
       <c r="AL58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM58" s="3">
-        <v>0</v>
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
         <v>125000</v>
-      </c>
-      <c r="AO58" s="3">
-        <v>124900</v>
       </c>
       <c r="AP58" s="3">
         <v>124900</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>124900</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>656600</v>
+      </c>
+      <c r="E59" s="3">
         <v>634400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>590000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>534300</v>
       </c>
-      <c r="G59" s="3">
-        <v>564800</v>
-      </c>
       <c r="H59" s="3">
+        <v>542100</v>
+      </c>
+      <c r="I59" s="3">
         <v>565400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>494600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>469400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>568200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>509900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>431400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>433800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>495300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>495900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>849100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>824600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1068400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>979200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>895600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>809700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1039100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>820200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>706300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>624000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>789600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>708600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>632700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>551900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>668900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>553300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>460400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>444800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>585500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>619900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>451700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>452100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>577700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>569000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>372700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>382800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1414800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1906600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1742800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1573800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1861200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1264300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1114300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>972400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1421800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1122400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>971200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>924000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2397800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1163000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1018900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>991700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1313400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1176800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1087800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>966800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1288000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1002600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>837900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>743900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1341000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1255000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1124800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1040900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>802600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>705200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>597900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>573300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>777300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>767300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>586000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>609400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>744900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>885900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>638200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>641800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3481600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2868600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2835100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2942400</v>
       </c>
-      <c r="G61" s="3">
-        <v>2922500</v>
-      </c>
       <c r="H61" s="3">
+        <v>2947100</v>
+      </c>
+      <c r="I61" s="3">
         <v>3602600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3828500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3763300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3538900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3689600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3835900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3873800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2433200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4287600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4105400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4064200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3793000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4167000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4156600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4165900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3887600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1737700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1770600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1776100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1387600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1679900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1449300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1368800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1470400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1194100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1143700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1053400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1203100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1222700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1292400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1102100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1141600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1081100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>249400</v>
+      </c>
+      <c r="E62" s="3">
         <v>250600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>165700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>182000</v>
       </c>
-      <c r="G62" s="3">
-        <v>178000</v>
-      </c>
       <c r="H62" s="3">
+        <v>153300</v>
+      </c>
+      <c r="I62" s="3">
         <v>154300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>133000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>132500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>152200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>113300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>94500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>88700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>95300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>94800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1140400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1131000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1143300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1184700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1123400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1141900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1135100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>857200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>815800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>815900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>814700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>776100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>685100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>667000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>480200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>456900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>443000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>430700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>379700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>352500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>367200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>284800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>299000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>272200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>262200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6104800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5960400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5760300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5667800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5889900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5917300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6002300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5810700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6074200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5948200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5932200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5958500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5992600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6433400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6264700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6186900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6249700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6528500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6367800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6274600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6310700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3597500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3424300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3335900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3543300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3711000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3259200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3076700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2753200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2336500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2235000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2147700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2210400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2322900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2175900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2186600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2146000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2299700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1981500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1891000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4553600</v>
+      </c>
+      <c r="E72" s="3">
         <v>4266700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4103300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3932500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3862500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3591400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3451400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3412000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3435100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3205300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3085900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3109800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3113000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2874500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2761300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2789100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2824000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2650900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2549100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2576600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2583800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2390200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2291800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2302100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2302600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2135100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2030100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2082000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2087700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1959900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1843800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1850000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1727000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1562600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1496300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1477000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1469400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1320800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1283500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1292400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2840500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2818800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2879200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2635100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2655100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2382300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2228300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2206400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2168200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2267200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2067600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2112700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2240600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1998900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1786600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1903700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1919100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1821000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1748100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1753800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1809100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1589300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1434000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1413800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1346500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1202500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1125400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1143400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1127500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1265600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1122600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1234000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1094300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1161800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1074000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1037900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1003800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>942300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>985800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1051300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>398100</v>
+      </c>
+      <c r="E81" s="3">
         <v>276300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>284600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>165400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>374200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>243100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>142400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>79800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>323200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>213700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>70300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>90900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>324100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>198500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>57500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>50400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>248100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>176600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>47200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>67200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>260400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>165000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>56300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>65800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>229700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>166800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>55900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>183300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>172200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>49900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>76700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>206800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>109100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>62100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>49900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>187100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>75900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>30100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E83" s="3">
         <v>74600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>75900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>75100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>120100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>69600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>68100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>68700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>52400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>53800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>52800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>52600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>75400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>76600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>78200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>82100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>83200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>89100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>76700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>48200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>48500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>47700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>49300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>47600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>44600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>42300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>42600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>43100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>40900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>40400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>38800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>37200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>36400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>37300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>677400</v>
+      </c>
+      <c r="E89" s="3">
         <v>301100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>324800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>42300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>699700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>360400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>236700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-125500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>721000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>207400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>189800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-62000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>729200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>175500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>123000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-204500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>457400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>80700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>40700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-135300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>450400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>106300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>127400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-44100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>442600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>144100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>98000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-86500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>398900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>135900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>177700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-95600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>418900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>132900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>235000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-93200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>353800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>167600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>81800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-87300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-18700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-17500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-21900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-29700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-33700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>84500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-139200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-104800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-226600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-102900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-210300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-40100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-71400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-29400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-36400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2588700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-21100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-35200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-96700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-244900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-86300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-384400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-71700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-92200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-44200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-41200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-46300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-59600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-45000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-508400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>113800</v>
+        <v>112800</v>
       </c>
       <c r="E96" s="3">
         <v>113800</v>
       </c>
       <c r="F96" s="3">
-        <v>103100</v>
+        <v>113800</v>
       </c>
       <c r="G96" s="3">
         <v>103100</v>
       </c>
       <c r="H96" s="3">
+        <v>103100</v>
+      </c>
+      <c r="I96" s="3">
         <v>103000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>102800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>93400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>94300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>94200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>94100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>85600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>85300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>85400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-85300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-75000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-74800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-74700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-74400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-66800</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-66600</v>
       </c>
       <c r="X96" s="3">
         <v>-66600</v>
       </c>
       <c r="Y96" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-66300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-61800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-62000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-61800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-55400</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-56100</v>
       </c>
       <c r="AF96" s="3">
         <v>-56100</v>
       </c>
       <c r="AG96" s="3">
+        <v>-56100</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-56500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-42500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-42800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-42500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-37900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-38600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-39600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-38500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-350600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-259500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-224200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-214200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-423300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-305200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>151800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-580400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-208900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-123500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>57300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-778000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-113600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-45900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>222800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-474400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-55600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-57800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>217000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2052900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-98500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-83900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-72700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-350400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>121100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>22400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>258100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-34300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-76900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-116100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>54200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-429700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-55600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-110700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>146100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-306800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-25900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>96100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>800</v>
       </c>
       <c r="K101" s="3">
         <v>800</v>
       </c>
       <c r="L101" s="3">
+        <v>800</v>
+      </c>
+      <c r="M101" s="3">
         <v>3600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>6000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-65900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>79900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-270800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>244300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>27300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>68800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-79300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>51500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>52900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-52600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-35600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>42200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-81300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-120000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>74500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>168100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-124300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>85100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>42300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>45200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-59300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-88200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-14400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>77700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>17700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>33800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>8300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-500300</v>
       </c>
     </row>
